--- a/2024AIDataScienceGNRClub/Advanced Excel/jan4.xlsx
+++ b/2024AIDataScienceGNRClub/Advanced Excel/jan4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E2088D-8853-43A4-A95C-A77506D55EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA75913E-4952-4085-92B2-A87C706FAA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00C455A7-C27C-4F8F-95DF-8AE123A1D978}"/>
   </bookViews>
@@ -139,9 +139,6 @@
     <t>AND</t>
   </si>
   <si>
-    <t>Birth Year</t>
-  </si>
-  <si>
     <t>Year (Short)</t>
   </si>
   <si>
@@ -182,6 +179,9 @@
   </si>
   <si>
     <t>Er</t>
+  </si>
+  <si>
+    <t>Year (Full)</t>
   </si>
 </sst>
 </file>
@@ -227,11 +227,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -848,29 +848,33 @@
     <col min="15" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>28</v>
       </c>
+      <c r="R1">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -895,44 +899,44 @@
         <v>36</v>
       </c>
       <c r="H3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>39</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>40</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>41</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
       </c>
       <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>45</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>46</v>
       </c>
-      <c r="S3" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>38036</v>
       </c>
       <c r="B4">
@@ -958,9 +962,57 @@
         <f>AND(E4=4, B4&gt;=10)</f>
         <v>0</v>
       </c>
+      <c r="H4" t="str">
+        <f>TEXT(A4, "yyyy")</f>
+        <v>2004</v>
+      </c>
+      <c r="I4" t="str">
+        <f>TEXT(A4, "yy")</f>
+        <v>04</v>
+      </c>
+      <c r="J4" t="str">
+        <f>TEXT(A4, "m")</f>
+        <v>2</v>
+      </c>
+      <c r="K4" t="str">
+        <f>TEXT(A4, "mm")</f>
+        <v>02</v>
+      </c>
+      <c r="L4" t="str">
+        <f>TEXT(A4, "mmm")</f>
+        <v>Feb</v>
+      </c>
+      <c r="M4" t="str">
+        <f>TEXT(A4, "mmmm")</f>
+        <v>February</v>
+      </c>
+      <c r="N4" t="str">
+        <f>TEXT(A4, "d")</f>
+        <v>19</v>
+      </c>
+      <c r="O4" t="str">
+        <f>TEXT(A4, "dd")</f>
+        <v>19</v>
+      </c>
+      <c r="P4" t="str">
+        <f>TEXT(A4, "ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>TEXT(A4, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="R4" t="str">
+        <f>TEXT(J4, "00")</f>
+        <v>02</v>
+      </c>
+      <c r="S4" t="str">
+        <f>TEXT(R1, "000")</f>
+        <v>012</v>
+      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>39091</v>
       </c>
       <c r="B5">
@@ -986,9 +1038,53 @@
         <f t="shared" ref="G5:G18" si="4">AND(E5=4, B5&gt;=10)</f>
         <v>0</v>
       </c>
+      <c r="H5" t="str">
+        <f t="shared" ref="H5:H18" si="5">TEXT(A5, "yyyy")</f>
+        <v>2007</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" ref="I5:I18" si="6">TEXT(A5, "yy")</f>
+        <v>07</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" ref="J5:J18" si="7">TEXT(A5, "m")</f>
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" ref="K5:K18" si="8">TEXT(A5, "mm")</f>
+        <v>01</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" ref="L5:L18" si="9">TEXT(A5, "mmm")</f>
+        <v>Jan</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" ref="M5:M18" si="10">TEXT(A5, "mmmm")</f>
+        <v>January</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" ref="N5:N18" si="11">TEXT(A5, "d")</f>
+        <v>9</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" ref="O5:O18" si="12">TEXT(A5, "dd")</f>
+        <v>09</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" ref="P5:P18" si="13">TEXT(A5, "ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" ref="Q5:Q18" si="14">TEXT(A5, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R18" si="15">TEXT(J5, "00")</f>
+        <v>01</v>
+      </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>39558</v>
       </c>
       <c r="B6">
@@ -1014,9 +1110,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H6" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="13"/>
+        <v>Sun</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="14"/>
+        <v>Sunday</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>40288</v>
       </c>
       <c r="B7">
@@ -1042,9 +1182,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H7" t="str">
+        <f t="shared" si="5"/>
+        <v>2010</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="13"/>
+        <v>Tue</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="14"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>39924</v>
       </c>
       <c r="B8">
@@ -1070,9 +1254,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H8" t="str">
+        <f t="shared" si="5"/>
+        <v>2009</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="6"/>
+        <v>09</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="13"/>
+        <v>Tue</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="14"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="R8" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>38829</v>
       </c>
       <c r="B9">
@@ -1098,9 +1326,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H9" t="str">
+        <f t="shared" si="5"/>
+        <v>2006</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="6"/>
+        <v>06</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>39561</v>
       </c>
       <c r="B10">
@@ -1126,9 +1398,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H10" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="11"/>
+        <v>23</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="13"/>
+        <v>Wed</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="14"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="R10" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>42148</v>
       </c>
       <c r="B11">
@@ -1154,9 +1470,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H11" t="str">
+        <f t="shared" si="5"/>
+        <v>2015</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="8"/>
+        <v>05</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="9"/>
+        <v>May</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="10"/>
+        <v>May</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="13"/>
+        <v>Sun</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="14"/>
+        <v>Sunday</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="15"/>
+        <v>05</v>
+      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>39807</v>
       </c>
       <c r="B12">
@@ -1182,9 +1542,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H12" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="9"/>
+        <v>Dec</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="10"/>
+        <v>December</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="13"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="14"/>
+        <v>Thursday</v>
+      </c>
+      <c r="R12" t="str">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>39655</v>
       </c>
       <c r="B13">
@@ -1210,9 +1614,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H13" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="8"/>
+        <v>07</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="9"/>
+        <v>Jul</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="10"/>
+        <v>July</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R13" t="str">
+        <f t="shared" si="15"/>
+        <v>07</v>
+      </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>39564</v>
       </c>
       <c r="B14">
@@ -1238,9 +1686,53 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H14" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R14" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>39809</v>
       </c>
       <c r="B15">
@@ -1266,9 +1758,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H15" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="9"/>
+        <v>Dec</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="10"/>
+        <v>December</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R15" t="str">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>39718</v>
       </c>
       <c r="B16">
@@ -1294,9 +1830,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="H16" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="8"/>
+        <v>09</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="9"/>
+        <v>Sep</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="10"/>
+        <v>September</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R16" t="str">
+        <f t="shared" si="15"/>
+        <v>09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>39688</v>
       </c>
       <c r="B17">
@@ -1322,9 +1902,53 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="H17" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="8"/>
+        <v>08</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="9"/>
+        <v>Aug</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="10"/>
+        <v>August</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="13"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="14"/>
+        <v>Thursday</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="15"/>
+        <v>08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>39507</v>
       </c>
       <c r="B18">
@@ -1350,48 +1974,92 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="H18" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="8"/>
+        <v>02</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="9"/>
+        <v>Feb</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="10"/>
+        <v>February</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="11"/>
+        <v>29</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="13"/>
+        <v>Fri</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="14"/>
+        <v>Friday</v>
+      </c>
+      <c r="R18" t="str">
+        <f t="shared" si="15"/>
+        <v>02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" t="str">
         <f>IF(AND(C21&gt;=30, C21&lt;=40), "Yes", "No")</f>
         <v>Yes</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" t="b">
         <f>OR(C24="Dr", C24="Prof")</f>
